--- a/Structure_Data/text.9.14/20260914_09/structure_factor_20260914_09.xlsx
+++ b/Structure_Data/text.9.14/20260914_09/structure_factor_20260914_09.xlsx
@@ -40,7 +40,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:D337"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -248,6 +248,3444 @@
         <v>27.4491082188406</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度 beta / Constrictivity (x)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈半径 r_min (um)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">孔体半径 r_max (um)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度状态 / Constrictivity Status</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">侵入入口 / Intrusion Inlet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球心邻域 / Center Connectivity</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">算法版本 / Method</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edt_critical_radii_closed_dilation_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半径采样 / Radius Sampling</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All positive EDT values</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius (um)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPSD (total volume fraction)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIP (total volume fraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0.248519897460938</v>
+      </c>
+      <c r="C30">
+        <v>0.246440887451172</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.5</v>
+      </c>
+      <c r="B31">
+        <v>0.248519897460938</v>
+      </c>
+      <c r="C31">
+        <v>0.246440887451172</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B32">
+        <v>0.108173370361328</v>
+      </c>
+      <c r="C32">
+        <v>0.00664901733398438</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B33">
+        <v>0.0133285522460938</v>
+      </c>
+      <c r="C33">
+        <v>0.00012969970703125</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>0.00500869750976562</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B35">
+        <v>0.002410888671875</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1.5</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弦长分布 / Chord Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_voxel_runs_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>29364</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>1.10931753167143</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>0.862727550207259</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axis</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Window-spanning lines</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full pore line policy</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one_period_censored</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.05</v>
+      </c>
+      <c r="B52">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.1</v>
+      </c>
+      <c r="B53">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.15</v>
+      </c>
+      <c r="B54">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.2</v>
+      </c>
+      <c r="B55">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.25</v>
+      </c>
+      <c r="B56">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.3</v>
+      </c>
+      <c r="B57">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.35</v>
+      </c>
+      <c r="B58">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.4</v>
+      </c>
+      <c r="B59">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.45</v>
+      </c>
+      <c r="B60">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.5</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.55</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.6</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.65</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.7</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.75</v>
+      </c>
+      <c r="B66">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.8</v>
+      </c>
+      <c r="B67">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.85</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.9</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.95</v>
+      </c>
+      <c r="B70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.5</v>
+      </c>
+      <c r="B72">
+        <v>13671</v>
+      </c>
+      <c r="C72">
+        <v>0.465570085819371</v>
+      </c>
+      <c r="D72">
+        <v>0.465570085819371</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>1</v>
+      </c>
+      <c r="B73">
+        <v>7095</v>
+      </c>
+      <c r="C73">
+        <v>0.241622394769105</v>
+      </c>
+      <c r="D73">
+        <v>0.707192480588476</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>1.5</v>
+      </c>
+      <c r="B74">
+        <v>3672</v>
+      </c>
+      <c r="C74">
+        <v>0.125051082958725</v>
+      </c>
+      <c r="D74">
+        <v>0.832243563547201</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>2</v>
+      </c>
+      <c r="B75">
+        <v>2186</v>
+      </c>
+      <c r="C75">
+        <v>0.0744448985151887</v>
+      </c>
+      <c r="D75">
+        <v>0.906688462062389</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>2.5</v>
+      </c>
+      <c r="B76">
+        <v>1162</v>
+      </c>
+      <c r="C76">
+        <v>0.0395722653589429</v>
+      </c>
+      <c r="D76">
+        <v>0.946260727421332</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>3</v>
+      </c>
+      <c r="B77">
+        <v>678</v>
+      </c>
+      <c r="C77">
+        <v>0.0230894973436861</v>
+      </c>
+      <c r="D77">
+        <v>0.969350224765018</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>3.5</v>
+      </c>
+      <c r="B78">
+        <v>383</v>
+      </c>
+      <c r="C78">
+        <v>0.0130431821277755</v>
+      </c>
+      <c r="D78">
+        <v>0.982393406892794</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>4</v>
+      </c>
+      <c r="B79">
+        <v>183</v>
+      </c>
+      <c r="C79">
+        <v>0.00623212096444626</v>
+      </c>
+      <c r="D79">
+        <v>0.98862552785724</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>4.5</v>
+      </c>
+      <c r="B80">
+        <v>130</v>
+      </c>
+      <c r="C80">
+        <v>0.00442718975616401</v>
+      </c>
+      <c r="D80">
+        <v>0.993052717613404</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>5</v>
+      </c>
+      <c r="B81">
+        <v>82</v>
+      </c>
+      <c r="C81">
+        <v>0.00279253507696499</v>
+      </c>
+      <c r="D81">
+        <v>0.995845252690369</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>5.5</v>
+      </c>
+      <c r="B82">
+        <v>51</v>
+      </c>
+      <c r="C82">
+        <v>0.00173682059664896</v>
+      </c>
+      <c r="D82">
+        <v>0.997582073287018</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>6</v>
+      </c>
+      <c r="B83">
+        <v>31</v>
+      </c>
+      <c r="C83">
+        <v>0.00105571448031603</v>
+      </c>
+      <c r="D83">
+        <v>0.998637787767334</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>6.5</v>
+      </c>
+      <c r="B84">
+        <v>15</v>
+      </c>
+      <c r="C84">
+        <v>0.000510829587249694</v>
+      </c>
+      <c r="D84">
+        <v>0.999148617354584</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>7</v>
+      </c>
+      <c r="B85">
+        <v>10</v>
+      </c>
+      <c r="C85">
+        <v>0.000340553058166462</v>
+      </c>
+      <c r="D85">
+        <v>0.99948917041275</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>7.5</v>
+      </c>
+      <c r="B86">
+        <v>8</v>
+      </c>
+      <c r="C86">
+        <v>0.00027244244653317</v>
+      </c>
+      <c r="D86">
+        <v>0.999761612859283</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>8</v>
+      </c>
+      <c r="B87">
+        <v>2</v>
+      </c>
+      <c r="C87">
+        <v>6.81106116332925e-05</v>
+      </c>
+      <c r="D87">
+        <v>0.999829723470917</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>8.5</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88">
+        <v>3.40553058166462e-05</v>
+      </c>
+      <c r="D88">
+        <v>0.999863778776733</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>9</v>
+      </c>
+      <c r="B89">
+        <v>2</v>
+      </c>
+      <c r="C89">
+        <v>6.81106116332925e-05</v>
+      </c>
+      <c r="D89">
+        <v>0.999931889388367</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>10</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90">
+        <v>3.40553058166462e-05</v>
+      </c>
+      <c r="D90">
+        <v>0.999965944694183</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>10.5</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91">
+        <v>3.40553058166462e-05</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92"/>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球接触分布 / Spherical Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_solid_to_pore_edt_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>196996</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>0.765430850169807</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>0.396413156721718</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance direction</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solid_to_pore</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance convention</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voxel_center_to_voxel_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>0.05</v>
+      </c>
+      <c r="B106">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>0.1</v>
+      </c>
+      <c r="B107">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>0.15</v>
+      </c>
+      <c r="B108">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>0.2</v>
+      </c>
+      <c r="B109">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>0.25</v>
+      </c>
+      <c r="B110">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>0.3</v>
+      </c>
+      <c r="B111">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>0.35</v>
+      </c>
+      <c r="B112">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>0.4</v>
+      </c>
+      <c r="B113">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>0.45</v>
+      </c>
+      <c r="B114">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>0.5</v>
+      </c>
+      <c r="B115">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>0.55</v>
+      </c>
+      <c r="B116">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>0.6</v>
+      </c>
+      <c r="B117">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>0.65</v>
+      </c>
+      <c r="B118">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>0.7</v>
+      </c>
+      <c r="B119">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>0.75</v>
+      </c>
+      <c r="B120">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>0.8</v>
+      </c>
+      <c r="B121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>0.85</v>
+      </c>
+      <c r="B122">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>0.9</v>
+      </c>
+      <c r="B123">
+        <v>1.22474487139159</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>0.95</v>
+      </c>
+      <c r="B124">
+        <v>1.58113883008419</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>0.5</v>
+      </c>
+      <c r="B126">
+        <v>95083</v>
+      </c>
+      <c r="C126">
+        <v>0.482664622631932</v>
+      </c>
+      <c r="D126">
+        <v>0.482664622631932</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B127">
+        <v>47161</v>
+      </c>
+      <c r="C127">
+        <v>0.239400800016244</v>
+      </c>
+      <c r="D127">
+        <v>0.722065422648176</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B128">
+        <v>11233</v>
+      </c>
+      <c r="C128">
+        <v>0.0570214623647181</v>
+      </c>
+      <c r="D128">
+        <v>0.779086885012894</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>1</v>
+      </c>
+      <c r="B129">
+        <v>8456</v>
+      </c>
+      <c r="C129">
+        <v>0.0429247294361307</v>
+      </c>
+      <c r="D129">
+        <v>0.822011614449024</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B130">
+        <v>12251</v>
+      </c>
+      <c r="C130">
+        <v>0.0621890799813194</v>
+      </c>
+      <c r="D130">
+        <v>0.884200694430344</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B131">
+        <v>4774</v>
+      </c>
+      <c r="C131">
+        <v>0.0242339945988751</v>
+      </c>
+      <c r="D131">
+        <v>0.908434689029219</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B132">
+        <v>2104</v>
+      </c>
+      <c r="C132">
+        <v>0.0106804199070032</v>
+      </c>
+      <c r="D132">
+        <v>0.919115108936222</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>1.5</v>
+      </c>
+      <c r="B133">
+        <v>3941</v>
+      </c>
+      <c r="C133">
+        <v>0.0200054823448192</v>
+      </c>
+      <c r="D133">
+        <v>0.939120591281041</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B134">
+        <v>2259</v>
+      </c>
+      <c r="C134">
+        <v>0.0114672379134602</v>
+      </c>
+      <c r="D134">
+        <v>0.950587829194501</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B135">
+        <v>1538</v>
+      </c>
+      <c r="C135">
+        <v>0.00780726512213446</v>
+      </c>
+      <c r="D135">
+        <v>0.958395094316636</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B136">
+        <v>463</v>
+      </c>
+      <c r="C136">
+        <v>0.00235030152896506</v>
+      </c>
+      <c r="D136">
+        <v>0.960745395845601</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B137">
+        <v>1289</v>
+      </c>
+      <c r="C137">
+        <v>0.00654328006660034</v>
+      </c>
+      <c r="D137">
+        <v>0.967288675912201</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B138">
+        <v>1669</v>
+      </c>
+      <c r="C138">
+        <v>0.00847225324372069</v>
+      </c>
+      <c r="D138">
+        <v>0.975760929155922</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>2</v>
+      </c>
+      <c r="B139">
+        <v>307</v>
+      </c>
+      <c r="C139">
+        <v>0.00155840727730512</v>
+      </c>
+      <c r="D139">
+        <v>0.977319336433227</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B140">
+        <v>1257</v>
+      </c>
+      <c r="C140">
+        <v>0.00638084022010599</v>
+      </c>
+      <c r="D140">
+        <v>0.983700176653333</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B141">
+        <v>610</v>
+      </c>
+      <c r="C141">
+        <v>0.00309650957379845</v>
+      </c>
+      <c r="D141">
+        <v>0.986796686227132</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B142">
+        <v>347</v>
+      </c>
+      <c r="C142">
+        <v>0.00176145708542305</v>
+      </c>
+      <c r="D142">
+        <v>0.988558143312555</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B143">
+        <v>282</v>
+      </c>
+      <c r="C143">
+        <v>0.00143150114723142</v>
+      </c>
+      <c r="D143">
+        <v>0.989989644459786</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B144">
+        <v>444</v>
+      </c>
+      <c r="C144">
+        <v>0.00225385287010904</v>
+      </c>
+      <c r="D144">
+        <v>0.992243497329895</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B145">
+        <v>182</v>
+      </c>
+      <c r="C145">
+        <v>0.000923876626936588</v>
+      </c>
+      <c r="D145">
+        <v>0.993167373956832</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>2.44948974278318</v>
+      </c>
+      <c r="B146">
+        <v>179</v>
+      </c>
+      <c r="C146">
+        <v>0.000908647891327743</v>
+      </c>
+      <c r="D146">
+        <v>0.994076021848159</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>2.5</v>
+      </c>
+      <c r="B147">
+        <v>201</v>
+      </c>
+      <c r="C147">
+        <v>0.0010203252857926</v>
+      </c>
+      <c r="D147">
+        <v>0.995096347133952</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>2.54950975679639</v>
+      </c>
+      <c r="B148">
+        <v>309</v>
+      </c>
+      <c r="C148">
+        <v>0.00156855976771102</v>
+      </c>
+      <c r="D148">
+        <v>0.996664906901663</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>2.59807621135332</v>
+      </c>
+      <c r="B149">
+        <v>105</v>
+      </c>
+      <c r="C149">
+        <v>0.00053300574630957</v>
+      </c>
+      <c r="D149">
+        <v>0.997197912647973</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>2.69258240356725</v>
+      </c>
+      <c r="B150">
+        <v>179</v>
+      </c>
+      <c r="C150">
+        <v>0.000908647891327743</v>
+      </c>
+      <c r="D150">
+        <v>0.9981065605393</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>2.73861278752583</v>
+      </c>
+      <c r="B151">
+        <v>82</v>
+      </c>
+      <c r="C151">
+        <v>0.000416252106641759</v>
+      </c>
+      <c r="D151">
+        <v>0.998522812645942</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>2.82842712474619</v>
+      </c>
+      <c r="B152">
+        <v>22</v>
+      </c>
+      <c r="C152">
+        <v>0.000111677394464862</v>
+      </c>
+      <c r="D152">
+        <v>0.998634490040407</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>2.87228132326901</v>
+      </c>
+      <c r="B153">
+        <v>72</v>
+      </c>
+      <c r="C153">
+        <v>0.000365489654612276</v>
+      </c>
+      <c r="D153">
+        <v>0.998999979695019</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>2.91547594742265</v>
+      </c>
+      <c r="B154">
+        <v>44</v>
+      </c>
+      <c r="C154">
+        <v>0.000223354788929724</v>
+      </c>
+      <c r="D154">
+        <v>0.999223334483949</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>2.95803989154981</v>
+      </c>
+      <c r="B155">
+        <v>32</v>
+      </c>
+      <c r="C155">
+        <v>0.000162439846494345</v>
+      </c>
+      <c r="D155">
+        <v>0.999385774330443</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>3</v>
+      </c>
+      <c r="B156">
+        <v>14</v>
+      </c>
+      <c r="C156">
+        <v>7.1067432841276e-05</v>
+      </c>
+      <c r="D156">
+        <v>0.999456841763285</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>3.04138126514911</v>
+      </c>
+      <c r="B157">
+        <v>8</v>
+      </c>
+      <c r="C157">
+        <v>4.06099616235863e-05</v>
+      </c>
+      <c r="D157">
+        <v>0.999497451724908</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>3.08220700148449</v>
+      </c>
+      <c r="B158">
+        <v>41</v>
+      </c>
+      <c r="C158">
+        <v>0.00020812605332088</v>
+      </c>
+      <c r="D158">
+        <v>0.999705577778229</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="B159">
+        <v>7</v>
+      </c>
+      <c r="C159">
+        <v>3.5533716420638e-05</v>
+      </c>
+      <c r="D159">
+        <v>0.99974111149465</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>3.20156211871642</v>
+      </c>
+      <c r="B160">
+        <v>26</v>
+      </c>
+      <c r="C160">
+        <v>0.000131982375276655</v>
+      </c>
+      <c r="D160">
+        <v>0.999873093869926</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>3.24037034920393</v>
+      </c>
+      <c r="B161">
+        <v>4</v>
+      </c>
+      <c r="C161">
+        <v>2.03049808117931e-05</v>
+      </c>
+      <c r="D161">
+        <v>0.999893398850738</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>3.278719262151</v>
+      </c>
+      <c r="B162">
+        <v>4</v>
+      </c>
+      <c r="C162">
+        <v>2.03049808117931e-05</v>
+      </c>
+      <c r="D162">
+        <v>0.99991370383155</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>3.3166247903554</v>
+      </c>
+      <c r="B163">
+        <v>4</v>
+      </c>
+      <c r="C163">
+        <v>2.03049808117931e-05</v>
+      </c>
+      <c r="D163">
+        <v>0.999934008812362</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>3.35410196624968</v>
+      </c>
+      <c r="B164">
+        <v>8</v>
+      </c>
+      <c r="C164">
+        <v>4.06099616235863e-05</v>
+      </c>
+      <c r="D164">
+        <v>0.999974618773985</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>3.39116499156263</v>
+      </c>
+      <c r="B165">
+        <v>2</v>
+      </c>
+      <c r="C165">
+        <v>1.01524904058966e-05</v>
+      </c>
+      <c r="D165">
+        <v>0.999984771264391</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>3.5</v>
+      </c>
+      <c r="B166">
+        <v>2</v>
+      </c>
+      <c r="C166">
+        <v>1.01524904058966e-05</v>
+      </c>
+      <c r="D166">
+        <v>0.999994923754797</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>3.53553390593274</v>
+      </c>
+      <c r="B167">
+        <v>1</v>
+      </c>
+      <c r="C167">
+        <v>5.07624520294828e-06</v>
+      </c>
+      <c r="D167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168"/>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两点相关函数 / Two-Point Correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_fft_radial_shells_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porosity</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>0.248519897460938</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radial bins</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bin_0_origin_only; bin_k: (k-1)*h &lt; distance &lt;= k*h</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normalization</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joint_probability; C(0)=porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius upper edge (um)</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displacement count</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean distance (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>0</v>
+      </c>
+      <c r="B179">
+        <v>0.248519897460938</v>
+      </c>
+      <c r="C179">
+        <v>1</v>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>0.5</v>
+      </c>
+      <c r="B180">
+        <v>0.139929453531901</v>
+      </c>
+      <c r="C180">
+        <v>6</v>
+      </c>
+      <c r="D180">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>1</v>
+      </c>
+      <c r="B181">
+        <v>0.106541853684645</v>
+      </c>
+      <c r="C181">
+        <v>26</v>
+      </c>
+      <c r="D181">
+        <v>0.82359556171208</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>1.5</v>
+      </c>
+      <c r="B182">
+        <v>0.07708740234375</v>
+      </c>
+      <c r="C182">
+        <v>90</v>
+      </c>
+      <c r="D182">
+        <v>1.31330283768748</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>2</v>
+      </c>
+      <c r="B183">
+        <v>0.0717745538967759</v>
+      </c>
+      <c r="C183">
+        <v>134</v>
+      </c>
+      <c r="D183">
+        <v>1.76619125712671</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>2.5</v>
+      </c>
+      <c r="B184">
+        <v>0.0757400157839753</v>
+      </c>
+      <c r="C184">
+        <v>258</v>
+      </c>
+      <c r="D184">
+        <v>2.25329087515144</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>3</v>
+      </c>
+      <c r="B185">
+        <v>0.0747574038621856</v>
+      </c>
+      <c r="C185">
+        <v>410</v>
+      </c>
+      <c r="D185">
+        <v>2.77015092047628</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>3.5</v>
+      </c>
+      <c r="B186">
+        <v>0.0725643760279605</v>
+      </c>
+      <c r="C186">
+        <v>494</v>
+      </c>
+      <c r="D186">
+        <v>3.26511495914839</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>4</v>
+      </c>
+      <c r="B187">
+        <v>0.0717138870902683</v>
+      </c>
+      <c r="C187">
+        <v>690</v>
+      </c>
+      <c r="D187">
+        <v>3.74137726298534</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>4.5</v>
+      </c>
+      <c r="B188">
+        <v>0.0709080924115409</v>
+      </c>
+      <c r="C188">
+        <v>962</v>
+      </c>
+      <c r="D188">
+        <v>4.25479734207796</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>5</v>
+      </c>
+      <c r="B189">
+        <v>0.0699069886476833</v>
+      </c>
+      <c r="C189">
+        <v>1098</v>
+      </c>
+      <c r="D189">
+        <v>4.75998893674797</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>5.5</v>
+      </c>
+      <c r="B190">
+        <v>0.0689216819969383</v>
+      </c>
+      <c r="C190">
+        <v>1406</v>
+      </c>
+      <c r="D190">
+        <v>5.25297061080461</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>6</v>
+      </c>
+      <c r="B191">
+        <v>0.0680250644079482</v>
+      </c>
+      <c r="C191">
+        <v>1578</v>
+      </c>
+      <c r="D191">
+        <v>5.7433060626392</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>6.5</v>
+      </c>
+      <c r="B192">
+        <v>0.0672081341474096</v>
+      </c>
+      <c r="C192">
+        <v>2018</v>
+      </c>
+      <c r="D192">
+        <v>6.24308779578354</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>7</v>
+      </c>
+      <c r="B193">
+        <v>0.0663974120207672</v>
+      </c>
+      <c r="C193">
+        <v>2342</v>
+      </c>
+      <c r="D193">
+        <v>6.75452277955052</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>7.5</v>
+      </c>
+      <c r="B194">
+        <v>0.0656837949991769</v>
+      </c>
+      <c r="C194">
+        <v>2634</v>
+      </c>
+      <c r="D194">
+        <v>7.25880828593797</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>8</v>
+      </c>
+      <c r="B195">
+        <v>0.0650411638383572</v>
+      </c>
+      <c r="C195">
+        <v>2930</v>
+      </c>
+      <c r="D195">
+        <v>7.7481595567505</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>8.5</v>
+      </c>
+      <c r="B196">
+        <v>0.0644450582944947</v>
+      </c>
+      <c r="C196">
+        <v>3402</v>
+      </c>
+      <c r="D196">
+        <v>8.24275983872338</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>9</v>
+      </c>
+      <c r="B197">
+        <v>0.0639336790530826</v>
+      </c>
+      <c r="C197">
+        <v>3926</v>
+      </c>
+      <c r="D197">
+        <v>8.74722614715433</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>9.5</v>
+      </c>
+      <c r="B198">
+        <v>0.0634259824399595</v>
+      </c>
+      <c r="C198">
+        <v>4266</v>
+      </c>
+      <c r="D198">
+        <v>9.24875254641385</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>10</v>
+      </c>
+      <c r="B199">
+        <v>0.0629871715198864</v>
+      </c>
+      <c r="C199">
+        <v>4730</v>
+      </c>
+      <c r="D199">
+        <v>9.74564847205822</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>10.5</v>
+      </c>
+      <c r="B200">
+        <v>0.0625877906536234</v>
+      </c>
+      <c r="C200">
+        <v>5510</v>
+      </c>
+      <c r="D200">
+        <v>10.2542063522575</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>11</v>
+      </c>
+      <c r="B201">
+        <v>0.0622465180990637</v>
+      </c>
+      <c r="C201">
+        <v>5562</v>
+      </c>
+      <c r="D201">
+        <v>10.7542478228895</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>11.5</v>
+      </c>
+      <c r="B202">
+        <v>0.0619554111998464</v>
+      </c>
+      <c r="C202">
+        <v>6410</v>
+      </c>
+      <c r="D202">
+        <v>11.244987895373</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>12</v>
+      </c>
+      <c r="B203">
+        <v>0.061702429470132</v>
+      </c>
+      <c r="C203">
+        <v>6894</v>
+      </c>
+      <c r="D203">
+        <v>11.7450714339387</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>12.5</v>
+      </c>
+      <c r="B204">
+        <v>0.061484723161155</v>
+      </c>
+      <c r="C204">
+        <v>7490</v>
+      </c>
+      <c r="D204">
+        <v>12.2441426243554</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <v>13</v>
+      </c>
+      <c r="B205">
+        <v>0.0612935292342582</v>
+      </c>
+      <c r="C205">
+        <v>8258</v>
+      </c>
+      <c r="D205">
+        <v>12.7444225452559</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>13.5</v>
+      </c>
+      <c r="B206">
+        <v>0.0611281663225788</v>
+      </c>
+      <c r="C206">
+        <v>8994</v>
+      </c>
+      <c r="D206">
+        <v>13.2528519154988</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>14</v>
+      </c>
+      <c r="B207">
+        <v>0.0610016995053813</v>
+      </c>
+      <c r="C207">
+        <v>9446</v>
+      </c>
+      <c r="D207">
+        <v>13.7542803671108</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>14.5</v>
+      </c>
+      <c r="B208">
+        <v>0.0609289633054536</v>
+      </c>
+      <c r="C208">
+        <v>9978</v>
+      </c>
+      <c r="D208">
+        <v>14.2483018118451</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>15</v>
+      </c>
+      <c r="B209">
+        <v>0.0608621844913142</v>
+      </c>
+      <c r="C209">
+        <v>11138</v>
+      </c>
+      <c r="D209">
+        <v>14.7478143756516</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>15.5</v>
+      </c>
+      <c r="B210">
+        <v>0.0608336435124349</v>
+      </c>
+      <c r="C210">
+        <v>11406</v>
+      </c>
+      <c r="D210">
+        <v>15.2452282287867</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>16</v>
+      </c>
+      <c r="B211">
+        <v>0.0608053224840411</v>
+      </c>
+      <c r="C211">
+        <v>12575</v>
+      </c>
+      <c r="D211">
+        <v>15.7433814113418</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>16.5</v>
+      </c>
+      <c r="B212">
+        <v>0.0608120404026131</v>
+      </c>
+      <c r="C212">
+        <v>12848</v>
+      </c>
+      <c r="D212">
+        <v>16.2480191911098</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>17</v>
+      </c>
+      <c r="B213">
+        <v>0.0608733036427158</v>
+      </c>
+      <c r="C213">
+        <v>12060</v>
+      </c>
+      <c r="D213">
+        <v>16.7498118527173</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>17.5</v>
+      </c>
+      <c r="B214">
+        <v>0.0609416909962741</v>
+      </c>
+      <c r="C214">
+        <v>11804</v>
+      </c>
+      <c r="D214">
+        <v>17.2477889982035</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>18</v>
+      </c>
+      <c r="B215">
+        <v>0.0610190511355819</v>
+      </c>
+      <c r="C215">
+        <v>11016</v>
+      </c>
+      <c r="D215">
+        <v>17.7466461218484</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>18.5</v>
+      </c>
+      <c r="B216">
+        <v>0.0610612338057188</v>
+      </c>
+      <c r="C216">
+        <v>10700</v>
+      </c>
+      <c r="D216">
+        <v>18.2476461964778</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>19</v>
+      </c>
+      <c r="B217">
+        <v>0.0611480339084702</v>
+      </c>
+      <c r="C217">
+        <v>9756</v>
+      </c>
+      <c r="D217">
+        <v>18.7461608461768</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>19.5</v>
+      </c>
+      <c r="B218">
+        <v>0.0612046183034429</v>
+      </c>
+      <c r="C218">
+        <v>9224</v>
+      </c>
+      <c r="D218">
+        <v>19.2443623593903</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>20</v>
+      </c>
+      <c r="B219">
+        <v>0.0612247922554343</v>
+      </c>
+      <c r="C219">
+        <v>8408</v>
+      </c>
+      <c r="D219">
+        <v>19.7427539394596</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>20.5</v>
+      </c>
+      <c r="B220">
+        <v>0.0612949887335588</v>
+      </c>
+      <c r="C220">
+        <v>7452</v>
+      </c>
+      <c r="D220">
+        <v>20.2349524648069</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>21</v>
+      </c>
+      <c r="B221">
+        <v>0.0612933733246543</v>
+      </c>
+      <c r="C221">
+        <v>7040</v>
+      </c>
+      <c r="D221">
+        <v>20.7366941177926</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>21.5</v>
+      </c>
+      <c r="B222">
+        <v>0.0613614688624221</v>
+      </c>
+      <c r="C222">
+        <v>5820</v>
+      </c>
+      <c r="D222">
+        <v>21.2419860619221</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>22</v>
+      </c>
+      <c r="B223">
+        <v>0.0613119860164455</v>
+      </c>
+      <c r="C223">
+        <v>4880</v>
+      </c>
+      <c r="D223">
+        <v>21.7372039907627</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>22.5</v>
+      </c>
+      <c r="B224">
+        <v>0.0613689558292792</v>
+      </c>
+      <c r="C224">
+        <v>3936</v>
+      </c>
+      <c r="D224">
+        <v>22.2302479362391</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>23</v>
+      </c>
+      <c r="B225">
+        <v>0.0613500754727487</v>
+      </c>
+      <c r="C225">
+        <v>2999</v>
+      </c>
+      <c r="D225">
+        <v>22.7334385317465</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>23.5</v>
+      </c>
+      <c r="B226">
+        <v>0.0613101539261844</v>
+      </c>
+      <c r="C226">
+        <v>2180</v>
+      </c>
+      <c r="D226">
+        <v>23.2369587045059</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>24</v>
+      </c>
+      <c r="B227">
+        <v>0.0611250182728709</v>
+      </c>
+      <c r="C227">
+        <v>1620</v>
+      </c>
+      <c r="D227">
+        <v>23.7279225769148</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>24.5</v>
+      </c>
+      <c r="B228">
+        <v>0.0608251900072919</v>
+      </c>
+      <c r="C228">
+        <v>1208</v>
+      </c>
+      <c r="D228">
+        <v>24.2151258882127</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>25</v>
+      </c>
+      <c r="B229">
+        <v>0.0606161145900718</v>
+      </c>
+      <c r="C229">
+        <v>942</v>
+      </c>
+      <c r="D229">
+        <v>24.7383759194601</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>25.5</v>
+      </c>
+      <c r="B230">
+        <v>0.0604799087733439</v>
+      </c>
+      <c r="C230">
+        <v>584</v>
+      </c>
+      <c r="D230">
+        <v>25.2823739766508</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>26</v>
+      </c>
+      <c r="B231">
+        <v>0.0603231242005254</v>
+      </c>
+      <c r="C231">
+        <v>284</v>
+      </c>
+      <c r="D231">
+        <v>25.7666230311241</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>26.5</v>
+      </c>
+      <c r="B232">
+        <v>0.0601173639297485</v>
+      </c>
+      <c r="C232">
+        <v>192</v>
+      </c>
+      <c r="D232">
+        <v>26.1687296580041</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>27</v>
+      </c>
+      <c r="B233">
+        <v>0.05994385939378</v>
+      </c>
+      <c r="C233">
+        <v>104</v>
+      </c>
+      <c r="D233">
+        <v>26.6774814912972</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>27.5</v>
+      </c>
+      <c r="B234">
+        <v>0.060064951578776</v>
+      </c>
+      <c r="C234">
+        <v>24</v>
+      </c>
+      <c r="D234">
+        <v>27.2129968013123</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>28</v>
+      </c>
+      <c r="B235">
+        <v>0.059661865234375</v>
+      </c>
+      <c r="C235">
+        <v>1</v>
+      </c>
+      <c r="D235">
+        <v>27.712812921102</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x displacement (um)</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>0</v>
+      </c>
+      <c r="B237">
+        <v>0.248519897460938</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>0.5</v>
+      </c>
+      <c r="B238">
+        <v>0.136505126953125</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>1</v>
+      </c>
+      <c r="B239">
+        <v>0.0944023132324219</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>1.5</v>
+      </c>
+      <c r="B240">
+        <v>0.0692939758300781</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>2</v>
+      </c>
+      <c r="B241">
+        <v>0.0783576965332031</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>2.5</v>
+      </c>
+      <c r="B242">
+        <v>0.0757484436035156</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>3</v>
+      </c>
+      <c r="B243">
+        <v>0.0739936828613281</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>3.5</v>
+      </c>
+      <c r="B244">
+        <v>0.0735282897949219</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>4</v>
+      </c>
+      <c r="B245">
+        <v>0.0722389221191406</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>4.5</v>
+      </c>
+      <c r="B246">
+        <v>0.0708045959472656</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>5</v>
+      </c>
+      <c r="B247">
+        <v>0.0692977905273438</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>5.5</v>
+      </c>
+      <c r="B248">
+        <v>0.0692596435546875</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>6</v>
+      </c>
+      <c r="B249">
+        <v>0.0681800842285156</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>6.5</v>
+      </c>
+      <c r="B250">
+        <v>0.0676231384277344</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>7</v>
+      </c>
+      <c r="B251">
+        <v>0.067230224609375</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>7.5</v>
+      </c>
+      <c r="B252">
+        <v>0.0672492980957031</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>8</v>
+      </c>
+      <c r="B253">
+        <v>0.0669784545898438</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>8.5</v>
+      </c>
+      <c r="B254">
+        <v>0.0660896301269531</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>9</v>
+      </c>
+      <c r="B255">
+        <v>0.065704345703125</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>9.5</v>
+      </c>
+      <c r="B256">
+        <v>0.0654067993164062</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>10</v>
+      </c>
+      <c r="B257">
+        <v>0.0654106140136719</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>10.5</v>
+      </c>
+      <c r="B258">
+        <v>0.0648918151855469</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>11</v>
+      </c>
+      <c r="B259">
+        <v>0.0640640258789062</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>11.5</v>
+      </c>
+      <c r="B260">
+        <v>0.0640106201171875</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>12</v>
+      </c>
+      <c r="B261">
+        <v>0.06341552734375</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>12.5</v>
+      </c>
+      <c r="B262">
+        <v>0.0621452331542969</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>13</v>
+      </c>
+      <c r="B263">
+        <v>0.0608749389648438</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>13.5</v>
+      </c>
+      <c r="B264">
+        <v>0.061309814453125</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>14</v>
+      </c>
+      <c r="B265">
+        <v>0.0623054504394531</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>14.5</v>
+      </c>
+      <c r="B266">
+        <v>0.06256103515625</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>15</v>
+      </c>
+      <c r="B267">
+        <v>0.0621528625488281</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>15.5</v>
+      </c>
+      <c r="B268">
+        <v>0.0616416931152344</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>16</v>
+      </c>
+      <c r="B269">
+        <v>0.061737060546875</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y displacement (um)</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>0</v>
+      </c>
+      <c r="B271">
+        <v>0.248519897460938</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>0.5</v>
+      </c>
+      <c r="B272">
+        <v>0.136543273925781</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>1</v>
+      </c>
+      <c r="B273">
+        <v>0.0938873291015625</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>1.5</v>
+      </c>
+      <c r="B274">
+        <v>0.0688819885253906</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>2</v>
+      </c>
+      <c r="B275">
+        <v>0.0783119201660156</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>2.5</v>
+      </c>
+      <c r="B276">
+        <v>0.0761795043945312</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>3</v>
+      </c>
+      <c r="B277">
+        <v>0.0735206604003906</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>3.5</v>
+      </c>
+      <c r="B278">
+        <v>0.0732650756835938</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>4</v>
+      </c>
+      <c r="B279">
+        <v>0.0730171203613281</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>4.5</v>
+      </c>
+      <c r="B280">
+        <v>0.0717735290527344</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>5</v>
+      </c>
+      <c r="B281">
+        <v>0.0702667236328125</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>5.5</v>
+      </c>
+      <c r="B282">
+        <v>0.0687179565429688</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>6</v>
+      </c>
+      <c r="B283">
+        <v>0.0685348510742188</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>6.5</v>
+      </c>
+      <c r="B284">
+        <v>0.0681343078613281</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>7</v>
+      </c>
+      <c r="B285">
+        <v>0.0673637390136719</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>7.5</v>
+      </c>
+      <c r="B286">
+        <v>0.0657615661621094</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>8</v>
+      </c>
+      <c r="B287">
+        <v>0.0646400451660156</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>8.5</v>
+      </c>
+      <c r="B288">
+        <v>0.0643539428710938</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>9</v>
+      </c>
+      <c r="B289">
+        <v>0.0644912719726562</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>9.5</v>
+      </c>
+      <c r="B290">
+        <v>0.0641822814941406</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>10</v>
+      </c>
+      <c r="B291">
+        <v>0.0631103515625</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>10.5</v>
+      </c>
+      <c r="B292">
+        <v>0.0620574951171875</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>11</v>
+      </c>
+      <c r="B293">
+        <v>0.0616226196289062</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>11.5</v>
+      </c>
+      <c r="B294">
+        <v>0.0613136291503906</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>12</v>
+      </c>
+      <c r="B295">
+        <v>0.0607528686523438</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>12.5</v>
+      </c>
+      <c r="B296">
+        <v>0.0603981018066406</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>13</v>
+      </c>
+      <c r="B297">
+        <v>0.0601806640625</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>13.5</v>
+      </c>
+      <c r="B298">
+        <v>0.0599784851074219</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>14</v>
+      </c>
+      <c r="B299">
+        <v>0.0606040954589844</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>14.5</v>
+      </c>
+      <c r="B300">
+        <v>0.0600547790527344</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>15</v>
+      </c>
+      <c r="B301">
+        <v>0.0599098205566406</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>15.5</v>
+      </c>
+      <c r="B302">
+        <v>0.0601119995117187</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>16</v>
+      </c>
+      <c r="B303">
+        <v>0.0605239868164062</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z displacement (um)</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>0</v>
+      </c>
+      <c r="B305">
+        <v>0.248519897460938</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>0.5</v>
+      </c>
+      <c r="B306">
+        <v>0.146739959716797</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>1</v>
+      </c>
+      <c r="B307">
+        <v>0.0990219116210938</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>1.5</v>
+      </c>
+      <c r="B308">
+        <v>0.0707855224609375</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>2</v>
+      </c>
+      <c r="B309">
+        <v>0.0747871398925781</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>2.5</v>
+      </c>
+      <c r="B310">
+        <v>0.0742874145507812</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>3</v>
+      </c>
+      <c r="B311">
+        <v>0.074127197265625</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>3.5</v>
+      </c>
+      <c r="B312">
+        <v>0.0721817016601562</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>4</v>
+      </c>
+      <c r="B313">
+        <v>0.070465087890625</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <v>4.5</v>
+      </c>
+      <c r="B314">
+        <v>0.0690650939941406</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>5</v>
+      </c>
+      <c r="B315">
+        <v>0.0679473876953125</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>5.5</v>
+      </c>
+      <c r="B316">
+        <v>0.0669441223144531</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>6</v>
+      </c>
+      <c r="B317">
+        <v>0.0668563842773438</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>6.5</v>
+      </c>
+      <c r="B318">
+        <v>0.0663566589355469</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>7</v>
+      </c>
+      <c r="B319">
+        <v>0.066253662109375</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>7.5</v>
+      </c>
+      <c r="B320">
+        <v>0.0648880004882812</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>8</v>
+      </c>
+      <c r="B321">
+        <v>0.0633201599121094</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>8.5</v>
+      </c>
+      <c r="B322">
+        <v>0.0629768371582031</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>9</v>
+      </c>
+      <c r="B323">
+        <v>0.0633354187011719</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>9.5</v>
+      </c>
+      <c r="B324">
+        <v>0.063385009765625</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>10</v>
+      </c>
+      <c r="B325">
+        <v>0.0623931884765625</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>10.5</v>
+      </c>
+      <c r="B326">
+        <v>0.0615768432617188</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>11</v>
+      </c>
+      <c r="B327">
+        <v>0.0608444213867188</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>11.5</v>
+      </c>
+      <c r="B328">
+        <v>0.0610885620117188</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>12</v>
+      </c>
+      <c r="B329">
+        <v>0.0614738464355469</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>12.5</v>
+      </c>
+      <c r="B330">
+        <v>0.0611381530761719</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <v>13</v>
+      </c>
+      <c r="B331">
+        <v>0.0605812072753906</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <v>13.5</v>
+      </c>
+      <c r="B332">
+        <v>0.0601730346679688</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <v>14</v>
+      </c>
+      <c r="B333">
+        <v>0.0600166320800781</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>14.5</v>
+      </c>
+      <c r="B334">
+        <v>0.0601081848144531</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>15</v>
+      </c>
+      <c r="B335">
+        <v>0.0609092712402344</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>15.5</v>
+      </c>
+      <c r="B336">
+        <v>0.0616188049316406</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>16</v>
+      </c>
+      <c r="B337">
+        <v>0.0619888305664062</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>